--- a/Data/staff.xlsx
+++ b/Data/staff.xlsx
@@ -68,6 +68,9 @@
   </x:si>
   <x:si>
     <x:t>Défense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/staff/f858facb-494f-45cf-a1a1-9408594adac3.jpg</x:t>
   </x:si>
   <x:si>
     <x:t>/uploads/staff/70079f42-960d-4836-9025-89bb5c319d4b.jpg</x:t>
@@ -536,6 +539,29 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
     </x:row>

--- a/Data/staff.xlsx
+++ b/Data/staff.xlsx
@@ -70,10 +70,52 @@
     <x:t>Défense</x:t>
   </x:si>
   <x:si>
+    <x:t>/uploads/staff/70079f42-960d-4836-9025-89bb5c319d4b.jpg</x:t>
+  </x:si>
+  <x:si>
     <x:t>/uploads/staff/f858facb-494f-45cf-a1a1-9408594adac3.jpg</x:t>
   </x:si>
   <x:si>
-    <x:t>/uploads/staff/70079f42-960d-4836-9025-89bb5c319d4b.jpg</x:t>
+    <x:t>ab2c78ba072f44f0b46b978d7aa4e64b</x:t>
+  </x:si>
+  <x:si>
+    <x:t>062aa19aab9446ac82f5747adaab97db</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pacheco</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Damien</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Offense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Entraineur depuis plus de 2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/staff/c5634ae4-7b69-44d8-a15e-9e7342d3e36c.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/staff/5e958a58-2e36-401d-9c94-46139cd5303c.jpg</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corriveau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unité spéciale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>asdhaksdjhaskdjh</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bcc8769527e749429280ff3bed9cad0f</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/staff/277813a0-860c-43e1-afaa-33c7f1752acd.jpg</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -427,7 +469,7 @@
   <x:dimension ref="A1:G1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -450,7 +492,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -473,7 +515,7 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:7">
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
@@ -496,12 +538,12 @@
         <x:v>15</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:7">
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>16</x:v>
@@ -519,12 +561,12 @@
         <x:v>18</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:7">
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>16</x:v>
@@ -541,28 +583,98 @@
       <x:c r="G5" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
+      <x:c r="H5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="0">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
+      <x:c r="A7" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
+      <x:c r="A8" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/staff.xlsx
+++ b/Data/staff.xlsx
@@ -34,88 +34,13 @@
     <x:t>ResponsableDe</x:t>
   </x:si>
   <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
     <x:t>PhotoPath</x:t>
   </x:si>
   <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Coach</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/staff/8dbc72af-3d84-4901-8a7e-a0c6eac901d5.JPG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Element</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Dave</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Entraineur</x:t>
-  </x:si>
-  <x:si>
-    <x:t>O-Line</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/staff/7b345756-73d7-41f2-80b1-11c7373d5acb.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Défense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/staff/70079f42-960d-4836-9025-89bb5c319d4b.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/staff/f858facb-494f-45cf-a1a1-9408594adac3.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ab2c78ba072f44f0b46b978d7aa4e64b</x:t>
-  </x:si>
-  <x:si>
-    <x:t>062aa19aab9446ac82f5747adaab97db</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pacheco</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Damien</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Offense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Entraineur depuis plus de 2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/staff/c5634ae4-7b69-44d8-a15e-9e7342d3e36c.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/staff/5e958a58-2e36-401d-9c94-46139cd5303c.jpg</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corriveau</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brian</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Unité spéciale</x:t>
-  </x:si>
-  <x:si>
-    <x:t>asdhaksdjhaskdjh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>bcc8769527e749429280ff3bed9cad0f</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/staff/277813a0-860c-43e1-afaa-33c7f1752acd.jpg</x:t>
+    <x:t>NoFiche</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -466,7 +391,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G1"/>
+  <x:dimension ref="A1:I1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:9">
@@ -491,190 +416,11 @@
       <x:c r="G1" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:9">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
+      <x:c r="H1" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="I1" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:9">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:9">
-      <x:c r="A4" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:9">
-      <x:c r="A5" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I5" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:9">
-      <x:c r="A6" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="I6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:9">
-      <x:c r="A7" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="I7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:9">
-      <x:c r="A8" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I8" s="0" t="s">
-        <x:v>32</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/staff.xlsx
+++ b/Data/staff.xlsx
@@ -41,6 +41,21 @@
   </x:si>
   <x:si>
     <x:t>NoFiche</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Soignant</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>380092ef0ba545e79fa4dc65b1728c6c</x:t>
+  </x:si>
+  <x:si>
+    <x:t>/uploads/staff/085b45af-0a36-4908-b8f8-78b9a065aa5d.jpg</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -423,6 +438,35 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" spans="1:9">
+      <x:c r="A2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/staff.xlsx
+++ b/Data/staff.xlsx
@@ -43,19 +43,25 @@
     <x:t>NoFiche</x:t>
   </x:si>
   <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Soignant</x:t>
+    <x:t>CleUnique</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Test</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Entraineur</x:t>
   </x:si>
   <x:si>
     <x:t/>
   </x:si>
   <x:si>
-    <x:t>380092ef0ba545e79fa4dc65b1728c6c</x:t>
-  </x:si>
-  <x:si>
-    <x:t>/uploads/staff/085b45af-0a36-4908-b8f8-78b9a065aa5d.jpg</x:t>
+    <x:t>asdasdas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>d865ab17-67b9-4867-b104-afb8bd59f33c</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -406,10 +412,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:I1"/>
+  <x:dimension ref="A1:J1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:9">
+    <x:row r="1" spans="1:10">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -437,34 +443,40 @@
       <x:c r="I1" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
+      <x:c r="J1" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
-    <x:row r="2" spans="1:9">
+    <x:row r="2" spans="1:10">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/staff.xlsx
+++ b/Data/staff.xlsx
@@ -41,27 +41,6 @@
   </x:si>
   <x:si>
     <x:t>NoFiche</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CleUnique</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Test2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Test</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Entraineur</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>asdasdas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>d865ab17-67b9-4867-b104-afb8bd59f33c</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -412,10 +391,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J1"/>
+  <x:dimension ref="A1:I1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:10">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -442,41 +421,6 @@
       </x:c>
       <x:c r="I1" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:10">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J2" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
